--- a/backend/importverif/corrige/MODELE FORMATION A4 GROUPE 4-15 excel_corrige.xlsx
+++ b/backend/importverif/corrige/MODELE FORMATION A4 GROUPE 4-15 excel_corrige.xlsx
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
